--- a/documentation/Daniel Ike CAN Setup 260612.xlsx
+++ b/documentation/Daniel Ike CAN Setup 260612.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniike\Desktop\Personal\Supra Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9520c19c2c7015c6/Documents/GitHub/Roundie/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB63543-5911-45AE-BF3B-FBEDE989B7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BBCE5BCD-258B-4F9B-B468-304697B937F9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBCE5BCD-258B-4F9B-B468-304697B937F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -428,7 +426,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,15 +808,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74D4BFAA-24D7-4AEA-BE2E-2128F30B84C0}">
   <dimension ref="A1:S41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -827,7 +825,7 @@
       </c>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
@@ -883,7 +881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1</v>
       </c>
@@ -939,7 +937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -992,7 +990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1045,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D6" s="1"/>
       <c r="I6" t="s">
         <v>40</v>
@@ -1081,7 +1079,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D7" s="1"/>
       <c r="I7" t="s">
         <v>44</v>
@@ -1114,7 +1112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1170,7 +1168,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D9" s="1"/>
       <c r="I9" t="s">
         <v>53</v>
@@ -1206,7 +1204,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D10" s="1"/>
       <c r="I10" t="s">
         <v>56</v>
@@ -1242,7 +1240,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D11" s="1"/>
       <c r="I11" t="s">
         <v>59</v>
@@ -1278,7 +1276,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D12" s="1"/>
       <c r="I12" t="s">
         <v>62</v>
@@ -1314,7 +1312,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D13" s="1"/>
       <c r="I13" t="s">
         <v>65</v>
@@ -1350,7 +1348,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5</v>
       </c>
@@ -1403,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D15" s="1"/>
       <c r="I15" t="s">
         <v>72</v>
@@ -1439,7 +1437,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="D16" s="1"/>
       <c r="I16" t="s">
         <v>74</v>
@@ -1475,7 +1473,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:19">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>6</v>
       </c>
@@ -1531,7 +1529,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="2:19">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>7</v>
       </c>
@@ -1584,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:19">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D19" s="1"/>
       <c r="I19" t="s">
         <v>82</v>
@@ -1617,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:19">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D20" s="1"/>
       <c r="I20" s="2" t="s">
         <v>84</v>
@@ -1653,7 +1651,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="2:19">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>8</v>
       </c>
@@ -1709,7 +1707,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="2:19">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>9</v>
       </c>
@@ -1762,7 +1760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:19">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D23" s="1"/>
       <c r="I23" t="s">
         <v>95</v>
@@ -1798,7 +1796,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="2:19">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D24" s="1"/>
       <c r="I24" t="s">
         <v>99</v>
@@ -1834,7 +1832,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="2:19">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D25" s="1"/>
       <c r="I25" t="s">
         <v>103</v>
@@ -1870,7 +1868,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="2:19">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>10</v>
       </c>
@@ -1926,7 +1924,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="2:19">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D27" s="1"/>
       <c r="I27" t="s">
         <v>109</v>
@@ -1962,7 +1960,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="2:19">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D28" s="1"/>
       <c r="I28" t="s">
         <v>111</v>
@@ -1995,52 +1993,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:19">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="I31" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="2:19">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="I32" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="9:9">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="9:9">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I35" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="9:9">
+    <row r="36" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I36" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="9:9">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I37" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="9:9">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="9:9">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I39" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="9:9">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I40" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="9:9">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" t="s">
         <v>121</v>
       </c>
